--- a/Outputs/Lough_Neagh_Treated_Discharges.xlsx
+++ b/Outputs/Lough_Neagh_Treated_Discharges.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C352"/>
+  <dimension ref="A1:C320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5856,550 +5856,6 @@
         </is>
       </c>
     </row>
-    <row r="321">
-      <c r="A321" t="inlineStr">
-        <is>
-          <t>Ballymarlagh WwTW</t>
-        </is>
-      </c>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>Braid and Main</t>
-        </is>
-      </c>
-      <c r="C321" t="inlineStr">
-        <is>
-          <t>Deerfin Burn</t>
-        </is>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" t="inlineStr">
-        <is>
-          <t>Ballymena WwTW</t>
-        </is>
-      </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>Braid and Main</t>
-        </is>
-      </c>
-      <c r="C322" t="inlineStr">
-        <is>
-          <t>River Main (Slaght)</t>
-        </is>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" t="inlineStr">
-        <is>
-          <t>Buckna WwTW</t>
-        </is>
-      </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>Braid and Main</t>
-        </is>
-      </c>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t>Glen Burn</t>
-        </is>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" t="inlineStr">
-        <is>
-          <t>Cargan WwTW</t>
-        </is>
-      </c>
-      <c r="B324" t="inlineStr">
-        <is>
-          <t>Braid and Main</t>
-        </is>
-      </c>
-      <c r="C324" t="inlineStr">
-        <is>
-          <t>Glenravel Water</t>
-        </is>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" t="inlineStr">
-        <is>
-          <t>Carnbeg WwTW</t>
-        </is>
-      </c>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>Braid and Main</t>
-        </is>
-      </c>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>River Main (Glarryford)</t>
-        </is>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" t="inlineStr">
-        <is>
-          <t>Carnlough Road WwTW</t>
-        </is>
-      </c>
-      <c r="B326" t="inlineStr">
-        <is>
-          <t>Braid and Main</t>
-        </is>
-      </c>
-      <c r="C326" t="inlineStr">
-        <is>
-          <t>Priest's Burn</t>
-        </is>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" t="inlineStr">
-        <is>
-          <t>Clogh WwTW</t>
-        </is>
-      </c>
-      <c r="B327" t="inlineStr">
-        <is>
-          <t>Braid and Main</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>Clogh River</t>
-        </is>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" t="inlineStr">
-        <is>
-          <t>Cloghmills WwTW</t>
-        </is>
-      </c>
-      <c r="B328" t="inlineStr">
-        <is>
-          <t>Braid and Main</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>Cloghmills Water</t>
-        </is>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" t="inlineStr">
-        <is>
-          <t>Connaught Road 21 ST</t>
-        </is>
-      </c>
-      <c r="B329" t="inlineStr">
-        <is>
-          <t>Braid and Main</t>
-        </is>
-      </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>River Main (Randalstown)</t>
-        </is>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" t="inlineStr">
-        <is>
-          <t>Coolsythe Road 23 ST</t>
-        </is>
-      </c>
-      <c r="B330" t="inlineStr">
-        <is>
-          <t>Braid and Main</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>River Main (Randalstown)</t>
-        </is>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" t="inlineStr">
-        <is>
-          <t>Craigywarren WwTW</t>
-        </is>
-      </c>
-      <c r="B331" t="inlineStr">
-        <is>
-          <t>Braid and Main</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>Clogh River</t>
-        </is>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" t="inlineStr">
-        <is>
-          <t>Crankill ST</t>
-        </is>
-      </c>
-      <c r="B332" t="inlineStr">
-        <is>
-          <t>Braid and Main</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>Clogh River</t>
-        </is>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" t="inlineStr">
-        <is>
-          <t>Duneany WwTW</t>
-        </is>
-      </c>
-      <c r="B333" t="inlineStr">
-        <is>
-          <t>Braid and Main</t>
-        </is>
-      </c>
-      <c r="C333" t="inlineStr">
-        <is>
-          <t>River Main (Glarryford)</t>
-        </is>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" t="inlineStr">
-        <is>
-          <t>Dungonnell ST</t>
-        </is>
-      </c>
-      <c r="B334" t="inlineStr">
-        <is>
-          <t>Braid and Main</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>Glenravel Water</t>
-        </is>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="inlineStr">
-        <is>
-          <t>Dunloy WwTW</t>
-        </is>
-      </c>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>Braid and Main</t>
-        </is>
-      </c>
-      <c r="C335" t="inlineStr">
-        <is>
-          <t>River Main (Dunloy)</t>
-        </is>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" t="inlineStr">
-        <is>
-          <t>Glarryford South WwTW</t>
-        </is>
-      </c>
-      <c r="B336" t="inlineStr">
-        <is>
-          <t>Braid and Main</t>
-        </is>
-      </c>
-      <c r="C336" t="inlineStr">
-        <is>
-          <t>River Main (Cullybackey)</t>
-        </is>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" t="inlineStr">
-        <is>
-          <t>Grove Park WwTW</t>
-        </is>
-      </c>
-      <c r="B337" t="inlineStr">
-        <is>
-          <t>Braid and Main</t>
-        </is>
-      </c>
-      <c r="C337" t="inlineStr">
-        <is>
-          <t>Kells Water (Moorfields)</t>
-        </is>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" t="inlineStr">
-        <is>
-          <t>Killygore WwTW</t>
-        </is>
-      </c>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>Braid and Main</t>
-        </is>
-      </c>
-      <c r="C338" t="inlineStr">
-        <is>
-          <t>Clogh River</t>
-        </is>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" t="inlineStr">
-        <is>
-          <t>Killylane ST</t>
-        </is>
-      </c>
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>Braid and Main</t>
-        </is>
-      </c>
-      <c r="C339" t="inlineStr">
-        <is>
-          <t>Glenwhirry River</t>
-        </is>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" t="inlineStr">
-        <is>
-          <t>Martinstown WwTW</t>
-        </is>
-      </c>
-      <c r="B340" t="inlineStr">
-        <is>
-          <t>Braid and Main</t>
-        </is>
-      </c>
-      <c r="C340" t="inlineStr">
-        <is>
-          <t>Clogh River</t>
-        </is>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" t="inlineStr">
-        <is>
-          <t>Moorfields WwTW</t>
-        </is>
-      </c>
-      <c r="B341" t="inlineStr">
-        <is>
-          <t>Braid and Main</t>
-        </is>
-      </c>
-      <c r="C341" t="inlineStr">
-        <is>
-          <t>Kells Water (Moorfields)</t>
-        </is>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" t="inlineStr">
-        <is>
-          <t>Newtown-Crommelin WwTW</t>
-        </is>
-      </c>
-      <c r="B342" t="inlineStr">
-        <is>
-          <t>Braid and Main</t>
-        </is>
-      </c>
-      <c r="C342" t="inlineStr">
-        <is>
-          <t>Skerry Water</t>
-        </is>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" t="inlineStr">
-        <is>
-          <t>Oaklands Broughshane ST</t>
-        </is>
-      </c>
-      <c r="B343" t="inlineStr">
-        <is>
-          <t>Braid and Main</t>
-        </is>
-      </c>
-      <c r="C343" t="inlineStr">
-        <is>
-          <t>Artoges River</t>
-        </is>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" t="inlineStr">
-        <is>
-          <t>Old Green WwTW</t>
-        </is>
-      </c>
-      <c r="B344" t="inlineStr">
-        <is>
-          <t>Braid and Main</t>
-        </is>
-      </c>
-      <c r="C344" t="inlineStr">
-        <is>
-          <t>Kells Water (Kells)</t>
-        </is>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" t="inlineStr">
-        <is>
-          <t>Procklis WwTW</t>
-        </is>
-      </c>
-      <c r="B345" t="inlineStr">
-        <is>
-          <t>Braid and Main</t>
-        </is>
-      </c>
-      <c r="C345" t="inlineStr">
-        <is>
-          <t>River Main (Randalstown)</t>
-        </is>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" t="inlineStr">
-        <is>
-          <t>Racavan WwTW</t>
-        </is>
-      </c>
-      <c r="B346" t="inlineStr">
-        <is>
-          <t>Braid and Main</t>
-        </is>
-      </c>
-      <c r="C346" t="inlineStr">
-        <is>
-          <t>Braid River (Broughshane)</t>
-        </is>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" t="inlineStr">
-        <is>
-          <t>Railway View Three ST</t>
-        </is>
-      </c>
-      <c r="B347" t="inlineStr">
-        <is>
-          <t>Braid and Main</t>
-        </is>
-      </c>
-      <c r="C347" t="inlineStr">
-        <is>
-          <t>River Main (Cullybackey)</t>
-        </is>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" t="inlineStr">
-        <is>
-          <t>Skerry View WwTW</t>
-        </is>
-      </c>
-      <c r="B348" t="inlineStr">
-        <is>
-          <t>Braid and Main</t>
-        </is>
-      </c>
-      <c r="C348" t="inlineStr">
-        <is>
-          <t>Braid River (Broughshane)</t>
-        </is>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" t="inlineStr">
-        <is>
-          <t>Slaght WwTW</t>
-        </is>
-      </c>
-      <c r="B349" t="inlineStr">
-        <is>
-          <t>Braid and Main</t>
-        </is>
-      </c>
-      <c r="C349" t="inlineStr">
-        <is>
-          <t>River Main (Slaght)</t>
-        </is>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" t="inlineStr">
-        <is>
-          <t>Straid Ballymena WwTW</t>
-        </is>
-      </c>
-      <c r="B350" t="inlineStr">
-        <is>
-          <t>Braid and Main</t>
-        </is>
-      </c>
-      <c r="C350" t="inlineStr">
-        <is>
-          <t>River Main (Slaght)</t>
-        </is>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" t="inlineStr">
-        <is>
-          <t>Tullygrawley WwTW</t>
-        </is>
-      </c>
-      <c r="B351" t="inlineStr">
-        <is>
-          <t>Braid and Main</t>
-        </is>
-      </c>
-      <c r="C351" t="inlineStr">
-        <is>
-          <t>River Main (Cullybackey)</t>
-        </is>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" t="inlineStr">
-        <is>
-          <t>Tullymore Road 43-45 ST</t>
-        </is>
-      </c>
-      <c r="B352" t="inlineStr">
-        <is>
-          <t>Braid and Main</t>
-        </is>
-      </c>
-      <c r="C352" t="inlineStr">
-        <is>
-          <t>Artoges River</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
